--- a/DemoAssetList.xlsx
+++ b/DemoAssetList.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\summersspark\Desktop\AudioDesign\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\summersspark\Downloads\Audio09-Final-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEEC886-D6F4-4495-8771-C378FE32289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C062330B-2A1B-40A8-A91E-3AD97E051860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4929" yWindow="3343" windowWidth="24685" windowHeight="13148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3266" yWindow="2829" windowWidth="24685" windowHeight="13148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -624,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26.921875" customWidth="1"/>
@@ -633,34 +633,54 @@
     <col min="6" max="6" width="19.84375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
     <row r="2" spans="1:6" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>86</v>
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -672,7 +692,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
@@ -680,7 +700,7 @@
     </row>
     <row r="5" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -692,32 +712,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
+    <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
         <v>85</v>
@@ -743,7 +744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1073,7 +1074,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>72</v>
       </c>

--- a/DemoAssetList.xlsx
+++ b/DemoAssetList.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\summersspark\Downloads\Audio09-Final-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C062330B-2A1B-40A8-A91E-3AD97E051860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F50842D-F056-4BEA-8FA5-505632DCBB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3266" yWindow="2829" windowWidth="24685" windowHeight="13148" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7586" yWindow="694" windowWidth="24685" windowHeight="13149" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
   <si>
     <t>File Name</t>
   </si>
@@ -159,18 +160,6 @@
     <t>Window opening</t>
   </si>
   <si>
-    <t>SFX_Ghost_Popup.wav</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>Ghost sudden appearance</t>
-  </si>
-  <si>
-    <t>Event trigger</t>
-  </si>
-  <si>
     <t>SFX_UI_Click.wav</t>
   </si>
   <si>
@@ -234,12 +223,6 @@
     <t>Placement</t>
   </si>
   <si>
-    <t>VO_Window_Creak.wav</t>
-  </si>
-  <si>
-    <t>Wooden window creaking</t>
-  </si>
-  <si>
     <t>Window actor</t>
   </si>
   <si>
@@ -267,15 +250,6 @@
     <t>Corridor</t>
   </si>
   <si>
-    <t>VO_Ghost_Distant.wav</t>
-  </si>
-  <si>
-    <t>Distant ghost voices</t>
-  </si>
-  <si>
-    <t>Large room</t>
-  </si>
-  <si>
     <t>3D One-shot Dialogue / Events</t>
   </si>
   <si>
@@ -286,6 +260,24 @@
   </si>
   <si>
     <t>2D Interactive Music System</t>
+  </si>
+  <si>
+    <t>VO_Window_close.wav</t>
+  </si>
+  <si>
+    <t>Wired window closing</t>
+  </si>
+  <si>
+    <t>VO_Wind_hitting_window.wav</t>
+  </si>
+  <si>
+    <t>wind's hitting window</t>
+  </si>
+  <si>
+    <t>near window</t>
+  </si>
+  <si>
+    <t>SFX_UI_Click2.wav</t>
   </si>
 </sst>
 </file>
@@ -635,7 +627,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
@@ -721,7 +713,7 @@
     <row r="6" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
@@ -764,7 +756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -784,7 +776,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -804,7 +796,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -824,7 +816,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -844,7 +836,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -864,7 +856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
@@ -884,7 +876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>44</v>
       </c>
@@ -904,9 +896,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
@@ -915,18 +907,18 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
@@ -940,98 +932,98 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
@@ -1051,15 +1043,15 @@
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>19</v>
@@ -1068,64 +1060,64 @@
         <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>81</v>

--- a/DemoAssetList.xlsx
+++ b/DemoAssetList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\summersspark\Downloads\Audio09-Final-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F50842D-F056-4BEA-8FA5-505632DCBB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC29C06-68BB-44E1-BE3C-EA9976074655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7586" yWindow="694" windowWidth="24685" windowHeight="13149" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
